--- a/data/ethanol_pathway_model.xlsx
+++ b/data/ethanol_pathway_model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d89659k\Documents\Research\ENGS 161 metabolic engineering course\2025 spring\Lectures\16 - Limits of product titer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\Dan Thinkpad P16\Documents (P16 laptop)\Research\Ctherm CBP project\AdhE protein engineering for novel pathway 2025\MDF analysis\mdf-ethanol-pathways\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A2DCD1-B90C-48BC-A074-289A9C0A3F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80EBC681-88F4-4138-8F67-70CA8DDB023D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31960" yWindow="1890" windowWidth="28800" windowHeight="17030" xr2:uid="{D0F5A4BD-C55E-4D74-8D67-1450C605B764}"/>
+    <workbookView xWindow="14303" yWindow="-6488" windowWidth="28995" windowHeight="17476" xr2:uid="{D0F5A4BD-C55E-4D74-8D67-1450C605B764}"/>
   </bookViews>
   <sheets>
     <sheet name="Reaction" sheetId="1" r:id="rId1"/>
@@ -32,12 +32,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="194">
   <si>
     <t>Flux</t>
   </si>
@@ -616,6 +619,9 @@
   </si>
   <si>
     <t>Cth malate shunt FNORp adhp</t>
+  </si>
+  <si>
+    <t>Net result --&gt;</t>
   </si>
 </sst>
 </file>
@@ -1060,23 +1066,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23983D60-ED86-442D-9585-E503671F62B9}">
-  <dimension ref="A1:BM35"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:BM37"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.86328125" customWidth="1"/>
-    <col min="2" max="2" width="15.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.06640625" customWidth="1"/>
-    <col min="4" max="4" width="55.796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.265625" style="1" customWidth="1"/>
-    <col min="6" max="34" width="4.06640625" customWidth="1"/>
-    <col min="35" max="35" width="10.9296875" customWidth="1"/>
-    <col min="36" max="46" width="7.46484375" customWidth="1"/>
-    <col min="47" max="50" width="7.46484375" style="1" customWidth="1"/>
-    <col min="51" max="58" width="6.73046875" style="1" customWidth="1"/>
-    <col min="59" max="61" width="6.73046875" customWidth="1"/>
+    <col min="1" max="1" width="29.88671875" customWidth="1"/>
+    <col min="2" max="2" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" customWidth="1"/>
+    <col min="4" max="4" width="55.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.21875" style="1" customWidth="1"/>
+    <col min="6" max="34" width="4.109375" customWidth="1"/>
+    <col min="35" max="35" width="10.88671875" customWidth="1"/>
+    <col min="36" max="46" width="7.44140625" customWidth="1"/>
+    <col min="47" max="50" width="7.44140625" style="1" customWidth="1"/>
+    <col min="51" max="58" width="6.77734375" style="1" customWidth="1"/>
+    <col min="59" max="61" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:65" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>150</v>
       </c>
@@ -1099,7 +1105,7 @@
       <c r="AW1"/>
       <c r="AX1"/>
     </row>
-    <row r="2" spans="1:65" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:65" x14ac:dyDescent="0.3">
       <c r="D2" s="16" t="s">
         <v>104</v>
       </c>
@@ -1152,7 +1158,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:65" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:65" x14ac:dyDescent="0.3">
       <c r="D3" s="16" t="s">
         <v>105</v>
       </c>
@@ -1205,7 +1211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:65" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:65" x14ac:dyDescent="0.3">
       <c r="D4" s="16" t="s">
         <v>176</v>
       </c>
@@ -1258,7 +1264,7 @@
         <v>1.88</v>
       </c>
     </row>
-    <row r="5" spans="1:65" ht="124.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:65" ht="124.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
@@ -1414,7 +1420,7 @@
       <c r="BL5" s="13"/>
       <c r="BM5" s="13"/>
     </row>
-    <row r="6" spans="1:65" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:65" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>94</v>
       </c>
@@ -1514,7 +1520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:65" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>94</v>
       </c>
@@ -1610,7 +1616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:65" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>94</v>
       </c>
@@ -1710,7 +1716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:65" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>94</v>
       </c>
@@ -1808,7 +1814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:65" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>94</v>
       </c>
@@ -1904,7 +1910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:65" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>94</v>
       </c>
@@ -2006,7 +2012,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:65" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:65" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
@@ -2106,7 +2112,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:65" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:65" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>94</v>
       </c>
@@ -2202,7 +2208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:65" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:65" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>94</v>
       </c>
@@ -2300,7 +2306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:65" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:65" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>94</v>
       </c>
@@ -2393,7 +2399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:65" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:65" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
         <v>95</v>
       </c>
@@ -2465,7 +2471,7 @@
       <c r="AS16" s="1"/>
       <c r="AT16" s="1"/>
     </row>
-    <row r="17" spans="1:50" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:50" x14ac:dyDescent="0.3">
       <c r="B17" s="5" t="s">
         <v>95</v>
       </c>
@@ -2535,7 +2541,7 @@
       <c r="AS17" s="1"/>
       <c r="AT17" s="1"/>
     </row>
-    <row r="18" spans="1:50" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:50" x14ac:dyDescent="0.3">
       <c r="B18" s="5" t="s">
         <v>95</v>
       </c>
@@ -2607,7 +2613,7 @@
       <c r="AS18" s="1"/>
       <c r="AT18" s="1"/>
     </row>
-    <row r="19" spans="1:50" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2708,7 +2714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:50" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:50" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="s">
         <v>106</v>
       </c>
@@ -2773,7 +2779,7 @@
       </c>
       <c r="AT20" s="1"/>
     </row>
-    <row r="21" spans="1:50" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:50" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
         <v>107</v>
       </c>
@@ -2842,7 +2848,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:50" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -2921,7 +2927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:50" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -2996,7 +3002,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="24" spans="1:50" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -3067,7 +3073,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:50" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -3143,7 +3149,7 @@
       <c r="AS25" s="1"/>
       <c r="AT25" s="1"/>
     </row>
-    <row r="26" spans="1:50" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:50" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
         <v>96</v>
       </c>
@@ -3212,7 +3218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:50" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -3285,7 +3291,7 @@
       <c r="AS27" s="1"/>
       <c r="AT27" s="1"/>
     </row>
-    <row r="28" spans="1:50" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:50" x14ac:dyDescent="0.3">
       <c r="B28" s="7" t="s">
         <v>96</v>
       </c>
@@ -3353,7 +3359,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:50" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -3443,7 +3449,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:50" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -3518,7 +3524,7 @@
       <c r="AS30" s="1"/>
       <c r="AT30" s="1"/>
     </row>
-    <row r="31" spans="1:50" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>68</v>
       </c>
@@ -3597,7 +3603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:50" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>70</v>
       </c>
@@ -3681,7 +3687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:46" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:46" x14ac:dyDescent="0.3">
       <c r="B33" s="8" t="s">
         <v>97</v>
       </c>
@@ -3746,7 +3752,7 @@
       <c r="AS33" s="1"/>
       <c r="AT33" s="1"/>
     </row>
-    <row r="34" spans="1:46" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>180</v>
       </c>
@@ -3816,7 +3822,7 @@
       <c r="AS34" s="1"/>
       <c r="AT34" s="1"/>
     </row>
-    <row r="35" spans="1:46" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>180</v>
       </c>
@@ -3885,6 +3891,127 @@
       <c r="AR35" s="1"/>
       <c r="AS35" s="1"/>
       <c r="AT35" s="1"/>
+    </row>
+    <row r="37" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="D37" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="F37">
+        <f>SUMPRODUCT($E$6:$E$35,F6:F35)</f>
+        <v>-1</v>
+      </c>
+      <c r="G37">
+        <f t="shared" ref="G37:AH37" si="1">SUMPRODUCT($E$6:$E$35,G6:G35)</f>
+        <v>2</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="1"/>
+        <v>-2</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="1"/>
+        <v>-2</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="AJ4:AX4">
@@ -3916,15 +4043,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACFC5460-E4D4-4127-A9B9-6F55DA9CD2DB}">
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.3984375" customWidth="1"/>
-    <col min="2" max="2" width="27.265625" customWidth="1"/>
-    <col min="3" max="3" width="10.9296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="99.73046875" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" customWidth="1"/>
+    <col min="2" max="2" width="27.21875" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="99.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -3934,7 +4061,7 @@
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>141</v>
       </c>
@@ -3954,7 +4081,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -3971,7 +4098,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>72</v>
       </c>
@@ -3988,7 +4115,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>73</v>
       </c>
@@ -4005,7 +4132,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>74</v>
       </c>
@@ -4022,7 +4149,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>75</v>
       </c>
@@ -4039,7 +4166,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>76</v>
       </c>
@@ -4056,7 +4183,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>78</v>
       </c>
@@ -4073,7 +4200,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>80</v>
       </c>
@@ -4090,7 +4217,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>81</v>
       </c>
@@ -4107,7 +4234,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>82</v>
       </c>
@@ -4124,7 +4251,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -4141,7 +4268,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>88</v>
       </c>
@@ -4158,7 +4285,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>86</v>
       </c>
@@ -4175,7 +4302,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>92</v>
       </c>
@@ -4195,7 +4322,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>90</v>
       </c>
@@ -4212,7 +4339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -4229,7 +4356,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -4246,7 +4373,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -4263,7 +4390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>89</v>
       </c>
@@ -4280,7 +4407,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -4297,7 +4424,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>77</v>
       </c>
@@ -4314,7 +4441,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -4331,7 +4458,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>91</v>
       </c>
@@ -4348,7 +4475,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>15</v>
       </c>
@@ -4368,7 +4495,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -4385,7 +4512,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -4402,7 +4529,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>83</v>
       </c>
@@ -4422,7 +4549,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>9</v>
       </c>
@@ -4442,7 +4569,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>6</v>
       </c>

--- a/data/ethanol_pathway_model.xlsx
+++ b/data/ethanol_pathway_model.xlsx
@@ -4482,14 +4482,14 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>0.001</v>
       </c>
       <c r="E31" t="n">
         <v>10</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Set to 10 mM, approximating dissolved CO2 in equilibrium with the fermentation gas phase. Dash et al. 2019 used a much lower value, which makes the malate shunt appear infeasible; Olson et al. 2017 showed that a ppdk deletion strain of C. thermocellum still produces ethanol, which requires the malate shunt, so the shunt must in fact be feasible.</t>
+          <t>Free over the default 0.001-10 mM range rather than fixed. Dash et al. 2019 used a low fixed value, at which the malate shunt is infeasible; Olson et al. 2017 showed a ppdk deletion strain still produces ethanol, which requires the malate shunt, so it must be feasible. Leaving CO2 free lets each pathway sit where its own thermodynamics allow. Note that CO2 is exchanged with the gas phase, so in a real fermentation all pathways would share one value.</t>
         </is>
       </c>
     </row>
